--- a/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Syracuse_20260220.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Syracuse_20260220.xlsx
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>16.08</v>
       </c>
       <c r="E5" t="n">
-        <v>241.2</v>
+        <v>112.56</v>
       </c>
     </row>
   </sheetData>
